--- a/Tabela_Funcionarios_Exemplo.xlsx
+++ b/Tabela_Funcionarios_Exemplo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NiD\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\material das aulas\Raimundos Curso planilhas Básico e Intermediário\Básico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F115BFE-E862-4D01-AAF3-C8B96C9A36CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1C2CC2E-740E-4085-ADD2-329C436E9475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Funcionarios" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
   </definedNames>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId4"/>
+    <pivotCache cacheId="8" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -37,12 +37,15 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="109">
   <si>
     <t>Unidade</t>
   </si>
@@ -1097,52 +1100,43 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Gráficos e tabelas dinâmicas'!$C$3:$C$18</c:f>
+              <c:f>'Gráficos e tabelas dinâmicas'!$C$3:$C$15</c:f>
               <c:strCache>
-                <c:ptCount val="15"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>Anderson</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Bruno</c:v>
+                  <c:v>Debora</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Caio</c:v>
+                  <c:v>Elisa</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Debora</c:v>
+                  <c:v>Gabriel</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Elisa</c:v>
+                  <c:v>João</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Gabriel</c:v>
+                  <c:v>Junior</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>Igor</c:v>
+                  <c:v>Maria</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>João</c:v>
+                  <c:v>Olivia</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>Junior</c:v>
+                  <c:v>Paula</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>Maria</c:v>
+                  <c:v>Raquel</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>Olivia</c:v>
+                  <c:v>Thais</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>Paula</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>Raquel</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>Thais</c:v>
-                </c:pt>
-                <c:pt idx="14">
                   <c:v>Vitória</c:v>
                 </c:pt>
               </c:strCache>
@@ -1150,54 +1144,45 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Gráficos e tabelas dinâmicas'!$D$3:$D$18</c:f>
+              <c:f>'Gráficos e tabelas dinâmicas'!$D$3:$D$15</c:f>
               <c:numCache>
                 <c:formatCode>\R\$\ #,##0.00</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8.5500000000000007</c:v>
+                  <c:v>11.059999999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>14.72</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>11.059999999999999</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.57</c:v>
+                  <c:v>6.69</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>16.32</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7.89</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>14.18</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>6.69</c:v>
-                </c:pt>
                 <c:pt idx="8">
-                  <c:v>18.38</c:v>
+                  <c:v>6.36</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>7.89</c:v>
+                  <c:v>9.91</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>1.78</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>6.36</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>9.91</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>1.78</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>21.78</c:v>
+                  <c:v>8.75</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1357,7 +1342,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1365,6 +1349,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1665,16 +1650,16 @@
                 <c:formatCode>\R\$\ #,##0.00</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>53.13</c:v>
+                  <c:v>49.81</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>1.78</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>29.09</c:v>
+                  <c:v>6.36</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>42.870000000000005</c:v>
+                  <c:v>40.81</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1820,7 +1805,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1828,6 +1812,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2156,16 +2141,16 @@
                 <c:formatCode>\R\$\ #,##0.00</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>35.15</c:v>
+                  <c:v>20.97</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>16.5</c:v>
+                  <c:v>1.78</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>20.150000000000002</c:v>
+                  <c:v>44.58</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>55.069999999999993</c:v>
+                  <c:v>31.43</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2332,7 +2317,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2340,6 +2324,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2778,7 +2763,7 @@
                   <c:v>7.15</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>35.61</c:v>
+                  <c:v>65.61</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>37.119999999999997</c:v>
@@ -2962,7 +2947,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2970,6 +2954,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:gradFill flip="none" rotWithShape="1">
@@ -3444,52 +3429,43 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Gráficos e tabelas dinâmicas'!$C$3:$C$18</c:f>
+              <c:f>'Gráficos e tabelas dinâmicas'!$C$3:$C$15</c:f>
               <c:strCache>
-                <c:ptCount val="15"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>Anderson</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Bruno</c:v>
+                  <c:v>Debora</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Caio</c:v>
+                  <c:v>Elisa</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Debora</c:v>
+                  <c:v>Gabriel</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Elisa</c:v>
+                  <c:v>João</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Gabriel</c:v>
+                  <c:v>Junior</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>Igor</c:v>
+                  <c:v>Maria</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>João</c:v>
+                  <c:v>Olivia</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>Junior</c:v>
+                  <c:v>Paula</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>Maria</c:v>
+                  <c:v>Raquel</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>Olivia</c:v>
+                  <c:v>Thais</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>Paula</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>Raquel</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>Thais</c:v>
-                </c:pt>
-                <c:pt idx="14">
                   <c:v>Vitória</c:v>
                 </c:pt>
               </c:strCache>
@@ -3497,54 +3473,45 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Gráficos e tabelas dinâmicas'!$D$3:$D$18</c:f>
+              <c:f>'Gráficos e tabelas dinâmicas'!$D$3:$D$15</c:f>
               <c:numCache>
                 <c:formatCode>\R\$\ #,##0.00</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8.5500000000000007</c:v>
+                  <c:v>11.059999999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>14.72</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>11.059999999999999</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.57</c:v>
+                  <c:v>6.69</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>16.32</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7.89</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>14.18</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>6.69</c:v>
-                </c:pt>
                 <c:pt idx="8">
-                  <c:v>18.38</c:v>
+                  <c:v>6.36</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>7.89</c:v>
+                  <c:v>9.91</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>1.78</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>6.36</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>9.91</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>1.78</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>21.78</c:v>
+                  <c:v>8.75</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3673,7 +3640,6 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3681,6 +3647,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4044,7 +4011,7 @@
                   <c:v>7.15</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>35.61</c:v>
+                  <c:v>65.61</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>37.119999999999997</c:v>
@@ -4231,7 +4198,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4239,6 +4205,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4617,16 +4584,16 @@
                 <c:formatCode>\R\$\ #,##0.00</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>53.13</c:v>
+                  <c:v>49.81</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>1.78</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>29.09</c:v>
+                  <c:v>6.36</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>42.870000000000005</c:v>
+                  <c:v>40.81</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4810,7 +4777,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4818,6 +4784,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4953,7 +4920,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="pt-BR"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -5417,16 +5384,16 @@
                 <c:formatCode>\R\$\ #,##0.00</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>35.15</c:v>
+                  <c:v>20.97</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>16.5</c:v>
+                  <c:v>1.78</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>20.150000000000002</c:v>
+                  <c:v>44.58</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>55.069999999999993</c:v>
+                  <c:v>31.43</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5593,7 +5560,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5601,6 +5567,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -11124,7 +11091,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="NiD" refreshedDate="46227.829307060187" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="21" xr:uid="{C1BBAAE8-029E-41C6-B806-FF6B22668586}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="NiD" refreshedDate="46248.660163194443" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="21" xr:uid="{C1BBAAE8-029E-41C6-B806-FF6B22668586}">
   <cacheSource type="worksheet">
     <worksheetSource name="Tabela2"/>
   </cacheSource>
@@ -11165,29 +11132,7 @@
       </sharedItems>
     </cacheField>
     <cacheField name="Data" numFmtId="0">
-      <sharedItems count="21">
-        <s v="27/10/2023"/>
-        <s v="12/10/2022"/>
-        <s v="11/12/2023"/>
-        <s v="12/04/2022"/>
-        <s v="19/03/2022"/>
-        <s v="01/11/2023"/>
-        <s v="27/10/2022"/>
-        <s v="10/10/2023"/>
-        <s v="28/01/2022"/>
-        <s v="18/02/2022"/>
-        <s v="23/05/2022"/>
-        <s v="16/11/2022"/>
-        <s v="25/06/2022"/>
-        <s v="29/11/2023"/>
-        <s v="29/06/2023"/>
-        <s v="23/08/2022"/>
-        <s v="05/01/2022"/>
-        <s v="08/09/2022"/>
-        <s v="27/09/2022"/>
-        <s v="15/04/2022"/>
-        <s v="03/10/2022"/>
-      </sharedItems>
+      <sharedItems/>
     </cacheField>
     <cacheField name="Horário Entrada" numFmtId="0">
       <sharedItems/>
@@ -11199,24 +11144,10 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="Horas Extras" numFmtId="0">
-      <sharedItems count="13">
-        <s v="00:25:48"/>
-        <s v="00:00:00"/>
-        <s v="00:44:24"/>
-        <s v="00:31:52"/>
-        <s v="00:12:39"/>
-        <s v="00:14:24"/>
-        <s v="00:07:55"/>
-        <s v="00:19:12"/>
-        <s v="00:24:14"/>
-        <s v="00:40:07"/>
-        <s v="00:05:02"/>
-        <s v="00:16:22"/>
-        <s v="00:39:55"/>
-      </sharedItems>
+      <sharedItems/>
     </cacheField>
     <cacheField name="Valor a Receber" numFmtId="164">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="16.32"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="30"/>
     </cacheField>
     <cacheField name="Ano" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2022" maxValue="2023" count="2">
@@ -11254,11 +11185,11 @@
     <x v="0"/>
     <x v="0"/>
     <x v="0"/>
-    <x v="0"/>
+    <s v="27/10/2023"/>
     <s v="07:45:00"/>
     <s v="18:10:48"/>
     <s v="10:25:48"/>
-    <x v="0"/>
+    <s v="00:25:48"/>
     <n v="8.5500000000000007"/>
     <x v="0"/>
     <x v="0"/>
@@ -11267,12 +11198,12 @@
     <x v="1"/>
     <x v="1"/>
     <x v="1"/>
-    <x v="1"/>
+    <s v="12/10/2022"/>
     <s v="08:00:00"/>
     <s v="18:00:00"/>
     <s v="10:00:00"/>
-    <x v="1"/>
-    <n v="0"/>
+    <s v="00:00:00"/>
+    <n v="30"/>
     <x v="1"/>
     <x v="0"/>
   </r>
@@ -11280,11 +11211,11 @@
     <x v="2"/>
     <x v="2"/>
     <x v="1"/>
-    <x v="2"/>
+    <s v="11/12/2023"/>
     <s v="07:30:00"/>
     <s v="18:14:24"/>
     <s v="10:44:24"/>
-    <x v="2"/>
+    <s v="00:44:24"/>
     <n v="14.72"/>
     <x v="0"/>
     <x v="1"/>
@@ -11293,11 +11224,11 @@
     <x v="2"/>
     <x v="3"/>
     <x v="2"/>
-    <x v="3"/>
+    <s v="12/04/2022"/>
     <s v="08:00:00"/>
     <s v="18:00:00"/>
     <s v="10:00:00"/>
-    <x v="1"/>
+    <s v="00:00:00"/>
     <n v="0"/>
     <x v="1"/>
     <x v="2"/>
@@ -11306,11 +11237,11 @@
     <x v="3"/>
     <x v="4"/>
     <x v="0"/>
-    <x v="4"/>
+    <s v="19/03/2022"/>
     <s v="08:00:00"/>
     <s v="18:00:00"/>
     <s v="10:00:00"/>
-    <x v="1"/>
+    <s v="00:00:00"/>
     <n v="0"/>
     <x v="1"/>
     <x v="3"/>
@@ -11319,11 +11250,11 @@
     <x v="0"/>
     <x v="5"/>
     <x v="1"/>
-    <x v="5"/>
+    <s v="01/11/2023"/>
     <s v="07:40:48"/>
     <s v="18:12:40"/>
     <s v="10:31:52"/>
-    <x v="3"/>
+    <s v="00:31:52"/>
     <n v="13.03"/>
     <x v="0"/>
     <x v="4"/>
@@ -11332,11 +11263,11 @@
     <x v="3"/>
     <x v="6"/>
     <x v="1"/>
-    <x v="6"/>
+    <s v="27/10/2022"/>
     <s v="08:01:45"/>
     <s v="18:14:24"/>
     <s v="10:12:39"/>
-    <x v="4"/>
+    <s v="00:12:39"/>
     <n v="5.17"/>
     <x v="1"/>
     <x v="0"/>
@@ -11345,11 +11276,11 @@
     <x v="1"/>
     <x v="1"/>
     <x v="1"/>
-    <x v="7"/>
+    <s v="10/10/2023"/>
     <s v="08:00:00"/>
     <s v="18:14:24"/>
     <s v="10:14:24"/>
-    <x v="5"/>
+    <s v="00:14:24"/>
     <n v="5.57"/>
     <x v="0"/>
     <x v="0"/>
@@ -11358,11 +11289,11 @@
     <x v="1"/>
     <x v="7"/>
     <x v="3"/>
-    <x v="8"/>
+    <s v="28/01/2022"/>
     <s v="08:00:00"/>
     <s v="18:07:55"/>
     <s v="10:07:55"/>
-    <x v="6"/>
+    <s v="00:07:55"/>
     <n v="2.8"/>
     <x v="1"/>
     <x v="5"/>
@@ -11371,11 +11302,11 @@
     <x v="1"/>
     <x v="8"/>
     <x v="1"/>
-    <x v="9"/>
+    <s v="18/02/2022"/>
     <s v="08:00:00"/>
     <s v="18:00:00"/>
     <s v="10:00:00"/>
-    <x v="1"/>
+    <s v="00:00:00"/>
     <n v="0"/>
     <x v="1"/>
     <x v="6"/>
@@ -11384,11 +11315,11 @@
     <x v="0"/>
     <x v="9"/>
     <x v="0"/>
-    <x v="10"/>
+    <s v="23/05/2022"/>
     <s v="07:40:48"/>
     <s v="18:00:00"/>
     <s v="10:19:12"/>
-    <x v="7"/>
+    <s v="00:19:12"/>
     <n v="6.36"/>
     <x v="1"/>
     <x v="7"/>
@@ -11397,11 +11328,11 @@
     <x v="3"/>
     <x v="10"/>
     <x v="3"/>
-    <x v="11"/>
+    <s v="16/11/2022"/>
     <s v="07:40:48"/>
     <s v="18:05:02"/>
     <s v="10:24:14"/>
-    <x v="8"/>
+    <s v="00:24:14"/>
     <n v="9.91"/>
     <x v="1"/>
     <x v="4"/>
@@ -11410,11 +11341,11 @@
     <x v="3"/>
     <x v="6"/>
     <x v="1"/>
-    <x v="12"/>
+    <s v="25/06/2022"/>
     <s v="08:00:00"/>
     <s v="18:14:24"/>
     <s v="10:14:24"/>
-    <x v="5"/>
+    <s v="00:14:24"/>
     <n v="5.89"/>
     <x v="1"/>
     <x v="8"/>
@@ -11423,11 +11354,11 @@
     <x v="3"/>
     <x v="11"/>
     <x v="0"/>
-    <x v="13"/>
+    <s v="29/11/2023"/>
     <s v="07:48:41"/>
     <s v="18:28:48"/>
     <s v="10:40:07"/>
-    <x v="9"/>
+    <s v="00:40:07"/>
     <n v="14.18"/>
     <x v="0"/>
     <x v="4"/>
@@ -11436,11 +11367,11 @@
     <x v="0"/>
     <x v="12"/>
     <x v="3"/>
-    <x v="14"/>
+    <s v="29/06/2023"/>
     <s v="08:00:00"/>
     <s v="18:05:02"/>
     <s v="10:05:02"/>
-    <x v="10"/>
+    <s v="00:05:02"/>
     <n v="2.06"/>
     <x v="0"/>
     <x v="8"/>
@@ -11449,11 +11380,11 @@
     <x v="1"/>
     <x v="13"/>
     <x v="3"/>
-    <x v="15"/>
+    <s v="23/08/2022"/>
     <s v="07:48:41"/>
     <s v="18:05:02"/>
     <s v="10:16:22"/>
-    <x v="11"/>
+    <s v="00:16:22"/>
     <n v="6.69"/>
     <x v="1"/>
     <x v="9"/>
@@ -11462,11 +11393,11 @@
     <x v="2"/>
     <x v="14"/>
     <x v="2"/>
-    <x v="16"/>
+    <s v="05/01/2022"/>
     <s v="08:00:00"/>
     <s v="18:05:02"/>
     <s v="10:05:02"/>
-    <x v="10"/>
+    <s v="00:05:02"/>
     <n v="1.78"/>
     <x v="1"/>
     <x v="5"/>
@@ -11475,11 +11406,11 @@
     <x v="0"/>
     <x v="5"/>
     <x v="1"/>
-    <x v="17"/>
+    <s v="08/09/2022"/>
     <s v="08:00:00"/>
     <s v="18:05:02"/>
     <s v="10:05:02"/>
-    <x v="10"/>
+    <s v="00:05:02"/>
     <n v="2.06"/>
     <x v="1"/>
     <x v="10"/>
@@ -11488,11 +11419,11 @@
     <x v="1"/>
     <x v="7"/>
     <x v="3"/>
-    <x v="18"/>
+    <s v="27/09/2022"/>
     <s v="08:00:00"/>
     <s v="18:14:24"/>
     <s v="10:14:24"/>
-    <x v="5"/>
+    <s v="00:14:24"/>
     <n v="5.09"/>
     <x v="1"/>
     <x v="10"/>
@@ -11501,11 +11432,11 @@
     <x v="0"/>
     <x v="5"/>
     <x v="1"/>
-    <x v="19"/>
+    <s v="15/04/2022"/>
     <s v="07:48:41"/>
     <s v="18:05:02"/>
     <s v="10:16:22"/>
-    <x v="11"/>
+    <s v="00:16:22"/>
     <n v="6.69"/>
     <x v="1"/>
     <x v="2"/>
@@ -11514,11 +11445,11 @@
     <x v="0"/>
     <x v="12"/>
     <x v="3"/>
-    <x v="20"/>
+    <s v="03/10/2022"/>
     <s v="07:28:00"/>
     <s v="18:07:55"/>
     <s v="10:39:55"/>
-    <x v="12"/>
+    <s v="00:39:55"/>
     <n v="16.32"/>
     <x v="1"/>
     <x v="0"/>
@@ -11527,7 +11458,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{09E5DA7F-123D-47C1-AA5D-5BEDF387E7C2}" name="Tabela dinâmica6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7" rowHeaderCaption="Setor">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{09E5DA7F-123D-47C1-AA5D-5BEDF387E7C2}" name="Tabela dinâmica6" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7" rowHeaderCaption="Setor">
   <location ref="E2:F7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField showAll="0">
@@ -11553,29 +11484,12 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="14">
-        <item x="1"/>
-        <item x="10"/>
-        <item x="6"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="11"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item x="12"/>
-        <item x="9"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField showAll="0"/>
     <pivotField dataField="1" numFmtId="164" showAll="0"/>
     <pivotField showAll="0">
       <items count="3">
         <item x="1"/>
-        <item x="0"/>
+        <item h="1" x="0"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -11649,7 +11563,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6556F177-95E3-4536-BCB1-4DE445678E5A}" name="Tabela dinâmica2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4" rowHeaderCaption="Local">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6556F177-95E3-4536-BCB1-4DE445678E5A}" name="Tabela dinâmica2" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4" rowHeaderCaption="Local">
   <location ref="C20:D25" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField axis="axisRow" showAll="0">
@@ -11672,7 +11586,7 @@
     <pivotField showAll="0">
       <items count="3">
         <item x="1"/>
-        <item x="0"/>
+        <item h="1" x="0"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -11746,18 +11660,10 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{29F2ECE7-9B3C-4742-90B7-008E28E61CA4}" name="Tabela dinâmica5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8" rowHeaderCaption="Funcionário">
-  <location ref="C2:D18" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{29F2ECE7-9B3C-4742-90B7-008E28E61CA4}" name="Tabela dinâmica5" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8" rowHeaderCaption="Funcionário">
+  <location ref="C2:D15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="3"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
       <items count="16">
         <item x="4"/>
@@ -11796,7 +11702,7 @@
     <pivotField showAll="0">
       <items count="3">
         <item x="1"/>
-        <item x="0"/>
+        <item h="1" x="0"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -11805,15 +11711,9 @@
   <rowFields count="1">
     <field x="1"/>
   </rowFields>
-  <rowItems count="16">
+  <rowItems count="13">
     <i>
       <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
     </i>
     <i>
       <x v="3"/>
@@ -11823,9 +11723,6 @@
     </i>
     <i>
       <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
     </i>
     <i>
       <x v="7"/>
@@ -11894,18 +11791,10 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EEF2C7F0-6769-47ED-9F0C-91A0C783EA4F}" name="Tabela dinâmica7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7" rowHeaderCaption="Mês">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EEF2C7F0-6769-47ED-9F0C-91A0C783EA4F}" name="Tabela dinâmica7" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7" rowHeaderCaption="Mês">
   <location ref="E13:F25" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="3"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -12040,7 +11929,7 @@
     <tabular pivotCacheId="1045585592">
       <items count="2">
         <i x="1" s="1"/>
-        <i x="0" s="1"/>
+        <i x="0"/>
       </items>
     </tabular>
   </data>
@@ -12387,22 +12276,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.44140625" customWidth="1"/>
-    <col min="3" max="3" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.88671875" customWidth="1"/>
-    <col min="6" max="6" width="13.88671875" customWidth="1"/>
+    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="13.109375" customWidth="1"/>
-    <col min="9" max="9" width="15.77734375" customWidth="1"/>
-    <col min="10" max="10" width="6.109375" customWidth="1"/>
-    <col min="11" max="11" width="6.33203125" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" customWidth="1"/>
+    <col min="9" max="9" width="15.7109375" customWidth="1"/>
+    <col min="10" max="10" width="6.140625" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -12437,7 +12326,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>11</v>
       </c>
@@ -12472,7 +12361,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>20</v>
       </c>
@@ -12498,7 +12387,7 @@
         <v>27</v>
       </c>
       <c r="I3" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J3" s="2">
         <v>2022</v>
@@ -12507,7 +12396,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>28</v>
       </c>
@@ -12542,7 +12431,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>28</v>
       </c>
@@ -12577,7 +12466,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>40</v>
       </c>
@@ -12612,7 +12501,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>11</v>
       </c>
@@ -12647,7 +12536,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>40</v>
       </c>
@@ -12682,7 +12571,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>20</v>
       </c>
@@ -12717,7 +12606,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>20</v>
       </c>
@@ -12752,7 +12641,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>20</v>
       </c>
@@ -12787,7 +12676,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
@@ -12822,7 +12711,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>40</v>
       </c>
@@ -12857,7 +12746,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>40</v>
       </c>
@@ -12892,7 +12781,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>40</v>
       </c>
@@ -12927,7 +12816,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>11</v>
       </c>
@@ -12962,7 +12851,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>20</v>
       </c>
@@ -12997,7 +12886,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>28</v>
       </c>
@@ -13032,7 +12921,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>11</v>
       </c>
@@ -13067,7 +12956,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>20</v>
       </c>
@@ -13102,7 +12991,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>11</v>
       </c>
@@ -13137,7 +13026,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>11</v>
       </c>
@@ -13183,20 +13072,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD9C144A-9CCC-4D06-9675-AA486EDCFF70}">
   <dimension ref="C2:F25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.88671875" customWidth="1"/>
-    <col min="3" max="3" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="22.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="24.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C2" s="13" t="s">
         <v>1</v>
       </c>
@@ -13210,7 +13099,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="3" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C3" s="14" t="s">
         <v>41</v>
       </c>
@@ -13221,15 +13110,15 @@
         <v>22</v>
       </c>
       <c r="F3" s="1">
-        <v>53.13</v>
+        <v>49.81</v>
       </c>
     </row>
-    <row r="4" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C4" s="14" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="D4" s="1">
-        <v>8.5500000000000007</v>
+        <v>11.059999999999999</v>
       </c>
       <c r="E4" s="14" t="s">
         <v>37</v>
@@ -13238,94 +13127,94 @@
         <v>1.78</v>
       </c>
     </row>
-    <row r="5" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C5" s="14" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D5" s="1">
-        <v>14.72</v>
+        <v>30</v>
       </c>
       <c r="E5" s="14" t="s">
         <v>13</v>
       </c>
       <c r="F5" s="1">
-        <v>29.09</v>
+        <v>6.36</v>
       </c>
     </row>
-    <row r="6" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C6" s="14" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="D6" s="1">
-        <v>11.059999999999999</v>
+        <v>0</v>
       </c>
       <c r="E6" s="14" t="s">
         <v>60</v>
       </c>
       <c r="F6" s="1">
-        <v>42.870000000000005</v>
+        <v>40.81</v>
       </c>
     </row>
-    <row r="7" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C7" s="14" t="s">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="D7" s="1">
-        <v>5.57</v>
+        <v>6.69</v>
       </c>
       <c r="E7" s="14" t="s">
         <v>106</v>
       </c>
       <c r="F7" s="1">
-        <v>126.87</v>
+        <v>98.76</v>
       </c>
     </row>
-    <row r="8" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C8" s="14" t="s">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="D8" s="1">
+        <v>16.32</v>
+      </c>
+    </row>
+    <row r="9" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C9" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" s="1">
+        <v>7.89</v>
+      </c>
+    </row>
+    <row r="10" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C10" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C9" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="D9" s="1">
-        <v>14.18</v>
+    <row r="11" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C11" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="D11" s="1">
+        <v>6.36</v>
       </c>
     </row>
-    <row r="10" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C10" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="D10" s="1">
-        <v>6.69</v>
+    <row r="12" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C12" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" s="1">
+        <v>9.91</v>
       </c>
     </row>
-    <row r="11" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C11" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="D11" s="1">
-        <v>18.38</v>
-      </c>
-    </row>
-    <row r="12" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C12" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D12" s="1">
-        <v>7.89</v>
-      </c>
-    </row>
-    <row r="13" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C13" s="14" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="D13" s="1">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="E13" s="13" t="s">
         <v>10</v>
@@ -13334,12 +13223,12 @@
         <v>107</v>
       </c>
     </row>
-    <row r="14" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C14" s="14" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="D14" s="1">
-        <v>6.36</v>
+        <v>8.75</v>
       </c>
       <c r="E14" s="14" t="s">
         <v>65</v>
@@ -13348,12 +13237,12 @@
         <v>4.58</v>
       </c>
     </row>
-    <row r="15" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C15" s="14" t="s">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="D15" s="1">
-        <v>9.91</v>
+        <v>98.759999999999991</v>
       </c>
       <c r="E15" s="14" t="s">
         <v>68</v>
@@ -13362,13 +13251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C16" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="D16" s="1">
-        <v>1.78</v>
-      </c>
+    <row r="16" spans="3:6" x14ac:dyDescent="0.25">
       <c r="E16" s="14" t="s">
         <v>43</v>
       </c>
@@ -13376,13 +13259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C17" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="D17" s="1">
-        <v>21.78</v>
-      </c>
+    <row r="17" spans="3:6" x14ac:dyDescent="0.25">
       <c r="E17" s="14" t="s">
         <v>39</v>
       </c>
@@ -13390,13 +13267,7 @@
         <v>6.69</v>
       </c>
     </row>
-    <row r="18" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C18" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="D18" s="1">
-        <v>126.86999999999999</v>
-      </c>
+    <row r="18" spans="3:6" x14ac:dyDescent="0.25">
       <c r="E18" s="14" t="s">
         <v>73</v>
       </c>
@@ -13404,7 +13275,7 @@
         <v>6.36</v>
       </c>
     </row>
-    <row r="19" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:6" x14ac:dyDescent="0.25">
       <c r="E19" s="14" t="s">
         <v>80</v>
       </c>
@@ -13412,7 +13283,7 @@
         <v>7.9499999999999993</v>
       </c>
     </row>
-    <row r="20" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C20" s="13" t="s">
         <v>108</v>
       </c>
@@ -13426,12 +13297,12 @@
         <v>6.69</v>
       </c>
     </row>
-    <row r="21" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C21" s="14" t="s">
         <v>40</v>
       </c>
       <c r="D21" s="1">
-        <v>35.15</v>
+        <v>20.97</v>
       </c>
       <c r="E21" s="14" t="s">
         <v>99</v>
@@ -13440,26 +13311,26 @@
         <v>7.15</v>
       </c>
     </row>
-    <row r="22" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C22" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D22" s="1">
-        <v>16.5</v>
+        <v>1.78</v>
       </c>
       <c r="E22" s="14" t="s">
         <v>19</v>
       </c>
       <c r="F22" s="1">
-        <v>35.61</v>
+        <v>65.61</v>
       </c>
     </row>
-    <row r="23" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C23" s="14" t="s">
         <v>20</v>
       </c>
       <c r="D23" s="1">
-        <v>20.150000000000002</v>
+        <v>44.58</v>
       </c>
       <c r="E23" s="14" t="s">
         <v>50</v>
@@ -13468,12 +13339,12 @@
         <v>37.119999999999997</v>
       </c>
     </row>
-    <row r="24" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C24" s="14" t="s">
         <v>11</v>
       </c>
       <c r="D24" s="1">
-        <v>55.069999999999993</v>
+        <v>31.43</v>
       </c>
       <c r="E24" s="14" t="s">
         <v>35</v>
@@ -13482,18 +13353,18 @@
         <v>14.72</v>
       </c>
     </row>
-    <row r="25" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C25" s="14" t="s">
         <v>106</v>
       </c>
       <c r="D25" s="1">
-        <v>126.86999999999999</v>
+        <v>98.759999999999991</v>
       </c>
       <c r="E25" s="14" t="s">
         <v>106</v>
       </c>
       <c r="F25" s="1">
-        <v>126.87</v>
+        <v>156.87</v>
       </c>
     </row>
   </sheetData>
@@ -13512,7 +13383,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{736FF3B9-0A2B-47A9-8816-7EA67725E1EF}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
